--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-resultat-examens-de-biologie-element-clinique-pertinent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8677" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8677" uniqueCount="740">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -754,6 +754,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.code.qualifier</t>
@@ -844,8 +848,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Valeur du résultat. Le type de valeur (attribut xsi:type) est choisi dynamiquement. Les autres attributs qui qualifient cette valeur (comme par exemple l'unité) dépendent du type de donnée choisi. Les résultats qualitatifs codés peuvent le cas échéant être exprimés dans plusieurs systèmes de codage simultanément. De même les résultats numériques peuvent être exprimés simultanément dans plusieurs unités.</t>
@@ -2038,8 +2042,8 @@
     <t>Observation.entryRelationship.observation.referenceRange.observationRange.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/BL
-http://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TS</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/IVL-INT
+http://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>ObservationRange.value</t>
@@ -7550,7 +7554,7 @@
         <v>74</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>74</v>
@@ -7558,17 +7562,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -7586,11 +7590,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7641,7 +7645,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7661,17 +7665,17 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -7692,10 +7696,10 @@
         <v>161</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7746,7 +7750,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7766,10 +7770,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7792,7 +7796,7 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -7845,7 +7849,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7865,10 +7869,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7944,7 +7948,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7964,10 +7968,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7993,10 +7997,10 @@
         <v>91</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8027,7 +8031,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -8045,7 +8049,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8065,10 +8069,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8091,13 +8095,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8148,7 +8152,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8168,10 +8172,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8194,7 +8198,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -8227,7 +8231,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -8245,7 +8249,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8265,10 +8269,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8291,7 +8295,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -8344,7 +8348,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8364,10 +8368,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8423,25 +8427,25 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8461,10 +8465,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8487,13 +8491,13 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8544,7 +8548,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8564,10 +8568,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8590,13 +8594,13 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8627,7 +8631,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -8645,7 +8649,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8665,10 +8669,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8691,13 +8695,13 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8728,7 +8732,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -8746,7 +8750,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8766,10 +8770,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8796,7 +8800,7 @@
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8847,7 +8851,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8867,10 +8871,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8893,7 +8897,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -8946,7 +8950,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8966,10 +8970,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8992,7 +8996,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -9045,7 +9049,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9065,10 +9069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9091,13 +9095,13 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9148,7 +9152,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9168,10 +9172,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9194,13 +9198,13 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9251,7 +9255,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9271,10 +9275,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9297,7 +9301,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -9350,7 +9354,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9370,10 +9374,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9396,10 +9400,10 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -9451,7 +9455,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9471,10 +9475,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9497,7 +9501,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -9538,7 +9542,7 @@
         <v>74</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
@@ -9548,7 +9552,7 @@
         <v>124</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9568,13 +9572,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
@@ -9596,13 +9600,13 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9653,7 +9657,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -9673,10 +9677,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9774,10 +9778,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9875,10 +9879,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9976,10 +9980,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10077,10 +10081,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10180,10 +10184,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10283,10 +10287,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10386,10 +10390,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10489,10 +10493,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10590,10 +10594,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10630,7 +10634,7 @@
         <v>74</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>74</v>
@@ -10649,7 +10653,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -10667,7 +10671,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -10687,10 +10691,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10717,7 +10721,7 @@
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10768,7 +10772,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -10788,10 +10792,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10818,12 +10822,12 @@
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
@@ -10869,7 +10873,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10889,10 +10893,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10968,7 +10972,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10988,10 +10992,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11014,7 +11018,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -11067,7 +11071,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11087,10 +11091,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11113,7 +11117,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -11166,7 +11170,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -11186,10 +11190,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11212,7 +11216,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -11265,7 +11269,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -11285,10 +11289,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11311,7 +11315,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -11364,7 +11368,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -11384,10 +11388,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11410,7 +11414,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -11463,7 +11467,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -11483,10 +11487,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11509,7 +11513,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -11562,7 +11566,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -11582,10 +11586,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11608,7 +11612,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -11661,7 +11665,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -11681,10 +11685,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11707,7 +11711,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -11760,7 +11764,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -11780,10 +11784,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11806,7 +11810,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -11859,7 +11863,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -11879,10 +11883,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11905,7 +11909,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -11958,7 +11962,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -11978,10 +11982,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12004,7 +12008,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -12057,7 +12061,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -12077,13 +12081,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>74</v>
@@ -12105,13 +12109,13 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12162,7 +12166,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -12182,10 +12186,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12283,10 +12287,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12384,10 +12388,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12485,10 +12489,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12586,10 +12590,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12689,10 +12693,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12792,10 +12796,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12895,10 +12899,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12998,10 +13002,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13099,10 +13103,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13139,7 +13143,7 @@
         <v>74</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>74</v>
@@ -13158,7 +13162,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>74</v>
@@ -13176,7 +13180,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -13196,10 +13200,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13226,7 +13230,7 @@
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13277,7 +13281,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -13297,10 +13301,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13327,12 +13331,12 @@
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -13378,7 +13382,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -13398,10 +13402,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13477,7 +13481,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -13497,10 +13501,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13523,7 +13527,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -13576,7 +13580,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -13596,10 +13600,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13622,7 +13626,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -13675,7 +13679,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -13695,10 +13699,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13721,7 +13725,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -13774,7 +13778,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13794,10 +13798,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13820,7 +13824,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13873,7 +13877,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13893,10 +13897,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13919,7 +13923,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13972,7 +13976,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13992,10 +13996,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14018,7 +14022,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -14071,7 +14075,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -14091,10 +14095,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14117,7 +14121,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -14170,7 +14174,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -14190,10 +14194,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14216,7 +14220,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -14269,7 +14273,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -14289,10 +14293,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14315,7 +14319,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -14368,7 +14372,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -14388,10 +14392,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14414,7 +14418,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -14467,7 +14471,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -14487,10 +14491,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14513,7 +14517,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -14566,7 +14570,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -14586,13 +14590,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>74</v>
@@ -14614,13 +14618,13 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14671,7 +14675,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -14691,10 +14695,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14792,10 +14796,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14893,10 +14897,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14994,10 +14998,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15095,10 +15099,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15198,10 +15202,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15301,10 +15305,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15404,10 +15408,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15507,10 +15511,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15608,10 +15612,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15648,7 +15652,7 @@
         <v>74</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>74</v>
@@ -15667,7 +15671,7 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>74</v>
@@ -15685,7 +15689,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -15705,10 +15709,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15735,7 +15739,7 @@
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15786,7 +15790,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -15806,10 +15810,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15836,12 +15840,12 @@
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
@@ -15887,7 +15891,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15907,10 +15911,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15986,7 +15990,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -16006,10 +16010,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16032,7 +16036,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -16085,7 +16089,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -16105,10 +16109,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16131,7 +16135,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -16184,7 +16188,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -16204,10 +16208,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16230,7 +16234,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -16283,7 +16287,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -16303,10 +16307,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16329,7 +16333,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -16382,7 +16386,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -16402,10 +16406,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16428,7 +16432,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -16481,7 +16485,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -16501,10 +16505,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16602,10 +16606,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16703,10 +16707,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16804,10 +16808,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16905,10 +16909,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17008,10 +17012,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17111,10 +17115,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17214,10 +17218,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17317,10 +17321,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17418,10 +17422,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17515,10 +17519,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17612,10 +17616,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17711,10 +17715,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17810,10 +17814,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17909,10 +17913,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17938,7 +17942,7 @@
         <v>161</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
@@ -18008,10 +18012,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18109,10 +18113,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18212,10 +18216,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18315,10 +18319,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18418,10 +18422,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18521,10 +18525,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18624,10 +18628,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18725,10 +18729,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18826,10 +18830,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18929,10 +18933,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19030,10 +19034,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19131,10 +19135,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19234,10 +19238,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19335,10 +19339,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19438,10 +19442,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19539,10 +19543,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19636,10 +19640,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19741,10 +19745,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19773,7 +19777,7 @@
       </c>
       <c r="L170" s="2"/>
       <c r="M170" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -19844,10 +19848,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19939,7 +19943,7 @@
         <v>74</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>74</v>
@@ -19947,17 +19951,17 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F172" t="s" s="2">
         <v>80</v>
@@ -19975,11 +19979,11 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -20030,7 +20034,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -20050,17 +20054,17 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F173" t="s" s="2">
         <v>80</v>
@@ -20082,7 +20086,7 @@
       </c>
       <c r="L173" s="2"/>
       <c r="M173" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -20133,7 +20137,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -20153,10 +20157,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20179,7 +20183,7 @@
         <v>74</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -20232,7 +20236,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -20252,10 +20256,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20331,7 +20335,7 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -20351,10 +20355,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20410,7 +20414,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>74</v>
@@ -20428,7 +20432,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -20448,10 +20452,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20549,10 +20553,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20593,7 +20597,7 @@
         <v>74</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>74</v>
@@ -20652,10 +20656,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20755,10 +20759,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20858,10 +20862,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20961,10 +20965,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -21064,10 +21068,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21165,10 +21169,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21266,10 +21270,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21369,17 +21373,17 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F186" t="s" s="2">
         <v>80</v>
@@ -21397,11 +21401,11 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -21452,7 +21456,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -21472,17 +21476,17 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F187" t="s" s="2">
         <v>80</v>
@@ -21504,7 +21508,7 @@
       </c>
       <c r="L187" s="2"/>
       <c r="M187" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -21555,7 +21559,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -21575,10 +21579,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21601,10 +21605,10 @@
         <v>74</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
@@ -21656,7 +21660,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -21676,10 +21680,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21702,7 +21706,7 @@
         <v>74</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21735,7 +21739,7 @@
       </c>
       <c r="Y189" s="2"/>
       <c r="Z189" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>74</v>
@@ -21753,7 +21757,7 @@
         <v>74</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -21773,10 +21777,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21799,7 +21803,7 @@
         <v>74</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
@@ -21852,7 +21856,7 @@
         <v>74</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -21872,10 +21876,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21931,25 +21935,25 @@
       </c>
       <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AA191" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF191" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -21969,10 +21973,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21995,10 +21999,10 @@
         <v>74</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
@@ -22050,7 +22054,7 @@
         <v>74</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -22070,10 +22074,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22096,7 +22100,7 @@
         <v>74</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -22129,7 +22133,7 @@
       </c>
       <c r="Y193" s="2"/>
       <c r="Z193" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>74</v>
@@ -22147,7 +22151,7 @@
         <v>74</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -22167,10 +22171,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22193,7 +22197,7 @@
         <v>74</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -22226,7 +22230,7 @@
       </c>
       <c r="Y194" s="2"/>
       <c r="Z194" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>74</v>
@@ -22244,7 +22248,7 @@
         <v>74</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -22264,10 +22268,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22294,7 +22298,7 @@
       </c>
       <c r="L195" s="2"/>
       <c r="M195" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -22345,7 +22349,7 @@
         <v>74</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -22365,10 +22369,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22391,7 +22395,7 @@
         <v>74</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -22444,7 +22448,7 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -22464,10 +22468,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22490,7 +22494,7 @@
         <v>74</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -22543,7 +22547,7 @@
         <v>74</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -22563,10 +22567,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22589,7 +22593,7 @@
         <v>74</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22642,7 +22646,7 @@
         <v>74</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -22662,10 +22666,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22688,7 +22692,7 @@
         <v>74</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22741,7 +22745,7 @@
         <v>74</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -22761,10 +22765,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22787,7 +22791,7 @@
         <v>74</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22840,7 +22844,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -22860,10 +22864,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22886,7 +22890,7 @@
         <v>74</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
@@ -22939,7 +22943,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -22959,10 +22963,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22985,7 +22989,7 @@
         <v>74</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -23038,7 +23042,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -23058,10 +23062,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -23084,7 +23088,7 @@
         <v>74</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -23137,7 +23141,7 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -23157,10 +23161,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -23183,7 +23187,7 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -23236,7 +23240,7 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -23256,10 +23260,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -23282,7 +23286,7 @@
         <v>74</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -23335,7 +23339,7 @@
         <v>74</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -23355,10 +23359,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23381,11 +23385,11 @@
         <v>74</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L206" s="2"/>
       <c r="M206" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -23436,7 +23440,7 @@
         <v>74</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -23456,10 +23460,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23557,10 +23561,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23658,10 +23662,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23759,10 +23763,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23860,10 +23864,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23963,10 +23967,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -24066,10 +24070,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24169,10 +24173,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24272,10 +24276,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24373,10 +24377,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24410,7 +24414,7 @@
       </c>
       <c r="Q216" s="2"/>
       <c r="R216" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="S216" t="s" s="2">
         <v>74</v>
@@ -24432,7 +24436,7 @@
       </c>
       <c r="Y216" s="2"/>
       <c r="Z216" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA216" t="s" s="2">
         <v>74</v>
@@ -24450,7 +24454,7 @@
         <v>74</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -24470,10 +24474,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24496,7 +24500,7 @@
         <v>74</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -24549,7 +24553,7 @@
         <v>74</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>75</v>
@@ -24569,10 +24573,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24670,10 +24674,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24771,10 +24775,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24872,10 +24876,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24973,10 +24977,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -25076,10 +25080,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -25179,10 +25183,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -25282,10 +25286,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25385,10 +25389,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25486,10 +25490,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25563,7 +25567,7 @@
         <v>74</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -25583,10 +25587,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25620,7 +25624,7 @@
       </c>
       <c r="Q228" s="2"/>
       <c r="R228" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="S228" t="s" s="2">
         <v>74</v>
@@ -25642,7 +25646,7 @@
       </c>
       <c r="Y228" s="2"/>
       <c r="Z228" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>74</v>
@@ -25660,7 +25664,7 @@
         <v>74</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
@@ -25680,10 +25684,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25739,7 +25743,7 @@
       </c>
       <c r="Y229" s="2"/>
       <c r="Z229" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>74</v>
@@ -25757,7 +25761,7 @@
         <v>74</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
@@ -25777,10 +25781,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25856,7 +25860,7 @@
         <v>74</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>80</v>
@@ -25876,10 +25880,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25902,7 +25906,7 @@
         <v>74</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
@@ -25955,7 +25959,7 @@
         <v>74</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -25975,10 +25979,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -26001,7 +26005,7 @@
         <v>74</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
@@ -26034,7 +26038,7 @@
       </c>
       <c r="Y232" s="2"/>
       <c r="Z232" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AA232" t="s" s="2">
         <v>74</v>
@@ -26052,7 +26056,7 @@
         <v>74</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
@@ -26072,10 +26076,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -26173,10 +26177,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26217,7 +26221,7 @@
         <v>74</v>
       </c>
       <c r="S234" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="T234" t="s" s="2">
         <v>74</v>
@@ -26276,10 +26280,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -26320,7 +26324,7 @@
         <v>74</v>
       </c>
       <c r="S235" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>74</v>
@@ -26379,10 +26383,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26482,10 +26486,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26585,10 +26589,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26688,10 +26692,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26789,10 +26793,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26890,10 +26894,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26993,17 +26997,17 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E242" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F242" t="s" s="2">
         <v>80</v>
@@ -27021,11 +27025,11 @@
         <v>74</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L242" s="2"/>
       <c r="M242" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -27076,7 +27080,7 @@
         <v>74</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>80</v>
@@ -27096,17 +27100,17 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E243" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F243" t="s" s="2">
         <v>80</v>
@@ -27128,7 +27132,7 @@
       </c>
       <c r="L243" s="2"/>
       <c r="M243" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -27179,7 +27183,7 @@
         <v>74</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -27199,10 +27203,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27225,11 +27229,11 @@
         <v>74</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L244" s="2"/>
       <c r="M244" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
@@ -27280,7 +27284,7 @@
         <v>74</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>80</v>
@@ -27300,10 +27304,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27401,10 +27405,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27502,10 +27506,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27603,10 +27607,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -27704,10 +27708,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -27807,10 +27811,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -27910,10 +27914,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -28013,10 +28017,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -28116,10 +28120,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -28217,10 +28221,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -28254,7 +28258,7 @@
       </c>
       <c r="Q254" s="2"/>
       <c r="R254" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="S254" t="s" s="2">
         <v>74</v>
@@ -28276,7 +28280,7 @@
       </c>
       <c r="Y254" s="2"/>
       <c r="Z254" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA254" t="s" s="2">
         <v>74</v>
@@ -28294,7 +28298,7 @@
         <v>74</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>80</v>
@@ -28314,10 +28318,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -28344,7 +28348,7 @@
       </c>
       <c r="L255" s="2"/>
       <c r="M255" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
@@ -28375,7 +28379,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>74</v>
@@ -28393,7 +28397,7 @@
         <v>74</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>75</v>
@@ -28413,10 +28417,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -28439,7 +28443,7 @@
         <v>74</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="L256" s="2"/>
       <c r="M256" s="2"/>
@@ -28492,7 +28496,7 @@
         <v>74</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>75</v>
@@ -28512,10 +28516,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -28538,7 +28542,7 @@
         <v>74</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L257" s="2"/>
       <c r="M257" s="2"/>
@@ -28591,7 +28595,7 @@
         <v>74</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>80</v>
@@ -28611,10 +28615,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -28637,7 +28641,7 @@
         <v>74</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L258" s="2"/>
       <c r="M258" s="2"/>
@@ -28690,7 +28694,7 @@
         <v>74</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>80</v>
@@ -28710,10 +28714,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -28736,7 +28740,7 @@
         <v>74</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L259" s="2"/>
       <c r="M259" s="2"/>
@@ -28789,7 +28793,7 @@
         <v>74</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>80</v>
@@ -28809,10 +28813,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -28835,7 +28839,7 @@
         <v>74</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L260" s="2"/>
       <c r="M260" s="2"/>
@@ -28888,7 +28892,7 @@
         <v>74</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>80</v>
@@ -28908,10 +28912,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -28934,7 +28938,7 @@
         <v>74</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L261" s="2"/>
       <c r="M261" s="2"/>
@@ -28987,7 +28991,7 @@
         <v>74</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>80</v>
@@ -29007,10 +29011,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -29033,7 +29037,7 @@
         <v>74</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L262" s="2"/>
       <c r="M262" s="2"/>
@@ -29086,7 +29090,7 @@
         <v>74</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>80</v>
@@ -29106,10 +29110,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -29132,7 +29136,7 @@
         <v>74</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L263" s="2"/>
       <c r="M263" s="2"/>
@@ -29185,7 +29189,7 @@
         <v>74</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>80</v>
@@ -29205,10 +29209,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -29231,7 +29235,7 @@
         <v>74</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L264" s="2"/>
       <c r="M264" s="2"/>
@@ -29284,7 +29288,7 @@
         <v>74</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>80</v>
@@ -29304,10 +29308,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -29330,7 +29334,7 @@
         <v>74</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L265" s="2"/>
       <c r="M265" s="2"/>
@@ -29383,7 +29387,7 @@
         <v>74</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>80</v>
@@ -29403,10 +29407,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -29429,7 +29433,7 @@
         <v>74</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L266" s="2"/>
       <c r="M266" s="2"/>
@@ -29482,7 +29486,7 @@
         <v>74</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>80</v>
@@ -29502,10 +29506,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -29528,11 +29532,11 @@
         <v>74</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L267" s="2"/>
       <c r="M267" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" s="2"/>
@@ -29583,7 +29587,7 @@
         <v>74</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>80</v>
@@ -29603,10 +29607,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -29704,10 +29708,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -29805,10 +29809,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -29906,10 +29910,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -30007,10 +30011,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -30110,10 +30114,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -30213,10 +30217,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -30316,10 +30320,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -30419,10 +30423,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -30520,10 +30524,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -30557,7 +30561,7 @@
       </c>
       <c r="Q277" s="2"/>
       <c r="R277" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="S277" t="s" s="2">
         <v>74</v>
@@ -30579,7 +30583,7 @@
       </c>
       <c r="Y277" s="2"/>
       <c r="Z277" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA277" t="s" s="2">
         <v>74</v>
@@ -30597,7 +30601,7 @@
         <v>74</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>80</v>
@@ -30617,10 +30621,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -30643,7 +30647,7 @@
         <v>74</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
@@ -30696,7 +30700,7 @@
         <v>74</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>75</v>
@@ -30716,10 +30720,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -30742,7 +30746,7 @@
         <v>74</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
@@ -30795,7 +30799,7 @@
         <v>74</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>80</v>
